--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-address.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-address.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-address.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>inseeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code|2.2.0}
 </t>
   </si>
   <si>
@@ -964,7 +964,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.15625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
